--- a/plantilla_inventario_POSmaster.xlsx
+++ b/plantilla_inventario_POSmaster.xlsx
@@ -1,42 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIS APP\POSmaster\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67D9CCA-4AEC-4399-B191-7BE8663E3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
     <sheet name="Proveedores (referencia)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+  <si>
+    <t>Nombre *</t>
+  </si>
+  <si>
+    <t>SKU *</t>
+  </si>
+  <si>
+    <t>Código de Barras</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Precio Venta *</t>
+  </si>
+  <si>
+    <t>Costo *</t>
+  </si>
+  <si>
+    <t>Stock Inicial</t>
+  </si>
+  <si>
+    <t>Stock Mínimo</t>
+  </si>
+  <si>
+    <t>IVA (%)</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Proveedor</t>
+  </si>
+  <si>
+    <t>Sede</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>Distribuidora XYZ</t>
+  </si>
+  <si>
+    <t>Sede Principal</t>
+  </si>
+  <si>
+    <t>Samsung Colombia</t>
+  </si>
+  <si>
+    <t>Nombre del Proveedor</t>
+  </si>
+  <si>
+    <t>NIT</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>900123456-1</t>
+  </si>
+  <si>
+    <t>3001234567</t>
+  </si>
+  <si>
+    <t>ventas@xyz.com</t>
+  </si>
+  <si>
+    <t>800654321-0</t>
+  </si>
+  <si>
+    <t>6017654321</t>
+  </si>
+  <si>
+    <t>💡 Esta hoja es de referencia — los proveedores de la columna "Proveedor" en la hoja Productos se crean automáticamente.</t>
+  </si>
+  <si>
+    <t>producto prueba</t>
+  </si>
+  <si>
+    <t>prueba</t>
+  </si>
+  <si>
+    <t>pruebainsumo</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,13 +153,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0832A3A0-99B4-4055-B076-CB153C9E9FA6}"/>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,308 +494,188 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.875" customWidth="1"/>
+    <col min="2" max="2" width="14.875" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="28.875" customWidth="1"/>
+    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="10.875" customWidth="1"/>
+    <col min="9" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="8.875" customWidth="1"/>
+    <col min="12" max="12" width="10.875" customWidth="1"/>
+    <col min="13" max="13" width="22.875" customWidth="1"/>
+    <col min="14" max="14" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre *</v>
-      </c>
-      <c r="B1" t="str">
-        <v>SKU *</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Código de Barras</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Categoría</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Marca</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Descripción</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Precio Venta *</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Costo *</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Stock Inicial</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Stock Mínimo</v>
-      </c>
-      <c r="K1" t="str">
-        <v>IVA (%)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Tipo</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Proveedor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Sede</v>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Camiseta Azul M</v>
-      </c>
-      <c r="B2" t="str">
-        <v>CAM-AZ-M</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>CAMISETAS</v>
-      </c>
-      <c r="E2" t="str">
-        <v>BRAND</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Camiseta algodón talla M</v>
-      </c>
-      <c r="G2" t="str">
-        <v>35000</v>
-      </c>
-      <c r="H2" t="str">
-        <v>18000</v>
-      </c>
-      <c r="I2" t="str">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <v>123456</v>
+      </c>
+      <c r="C2">
+        <v>987654321</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>250000</v>
+      </c>
+      <c r="H2">
+        <v>189000</v>
+      </c>
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" t="str">
-        <v>2</v>
-      </c>
-      <c r="K2" t="str">
-        <v>19</v>
-      </c>
-      <c r="L2" t="str">
-        <v>STANDARD</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Distribuidora XYZ</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Sede Principal</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Pantalla Samsung A11</v>
-      </c>
-      <c r="B3" t="str">
-        <v>SKU-001</v>
-      </c>
-      <c r="C3" t="str">
-        <v>7890123456789</v>
-      </c>
-      <c r="D3" t="str">
-        <v>PANTALLAS</v>
-      </c>
-      <c r="E3" t="str">
-        <v>SAMSUNG</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Pantalla original</v>
-      </c>
-      <c r="G3" t="str">
-        <v>45000</v>
-      </c>
-      <c r="H3" t="str">
-        <v>30000</v>
-      </c>
-      <c r="I3" t="str">
-        <v>4</v>
-      </c>
-      <c r="J3" t="str">
+      <c r="J2">
         <v>1</v>
       </c>
-      <c r="K3" t="str">
-        <v>19</v>
-      </c>
-      <c r="L3" t="str">
-        <v>STANDARD</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Samsung Colombia</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Sede Principal</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Servicio Técnico</v>
-      </c>
-      <c r="B4" t="str">
-        <v>SERV-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>SERVICIOS</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>Diagnóstico y reparación</v>
-      </c>
-      <c r="G4" t="str">
-        <v>50000</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="K2">
         <v>0</v>
       </c>
-      <c r="I4" t="str">
-        <v>0</v>
-      </c>
-      <c r="J4" t="str">
-        <v>0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0</v>
-      </c>
-      <c r="L4" t="str">
-        <v>SERVICE</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v>Sede Principal</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>💡 INSTRUCCIONES:</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>• Campos con * son obligatorios</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>• Tipo: STANDARD (normal) o SERVICE (servicio sin stock)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>• Proveedor: escribe el nombre exactamente — se crea automáticamente si no existe</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>• IVA: escribe solo el número (19, 5, 0)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>• Stock Inicial: cantidad en bodega al importar</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>• Sede: escribe el nombre exacto de la sede. Opciones disponibles: Odontología | Sede Principal | Tecnología / Celulares | Veterinaria / Farmacia</v>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
+    <ignoredError sqref="A1:N1 D10:N12 L2 N2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.875" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre del Proveedor</v>
-      </c>
-      <c r="B1" t="str">
-        <v>NIT</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Teléfono</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Email</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Distribuidora XYZ</v>
-      </c>
-      <c r="B2" t="str">
-        <v>900123456-1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>3001234567</v>
-      </c>
-      <c r="D2" t="str">
-        <v>ventas@xyz.com</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Samsung Colombia</v>
-      </c>
-      <c r="B3" t="str">
-        <v>800654321-0</v>
-      </c>
-      <c r="C3" t="str">
-        <v>6017654321</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>💡 Esta hoja es de referencia — los proveedores de la columna "Proveedor" en la hoja Productos se crean automáticamente.</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError sqref="A1:D5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/plantilla_inventario_POSmaster.xlsx
+++ b/plantilla_inventario_POSmaster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIS APP\POSmaster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67D9CCA-4AEC-4399-B191-7BE8663E3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF26E3F5-E230-4F45-958E-FE9A38314F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3180" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
@@ -577,13 +577,13 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="H2">
-        <v>189000</v>
+        <v>100000</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>1</v>
